--- a/sample-data/goc-ho-coffee/06_dia_diem_va_van_hanh.xlsx
+++ b/sample-data/goc-ho-coffee/06_dia_diem_va_van_hanh.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Địa điểm" sheetId="1" r:id="Rad9ec91eadfe4cce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhân sự lịch ca" sheetId="2" r:id="Ra4f2b097a4ae4c76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điện nước" sheetId="3" r:id="Rcebc6f9ab7b04040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Địa điểm" sheetId="1" r:id="Re17476d3f29141c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nhân sự lịch ca" sheetId="2" r:id="R1107dfcb18b64ea3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Điện nước" sheetId="3" r:id="R0b925cf8d03d422d"/>
   </x:sheets>
 </x:workbook>
 </file>
